--- a/cerdanyola_offer_candidates_400_700k.xlsx
+++ b/cerdanyola_offer_candidates_400_700k.xlsx
@@ -1361,27 +1361,23 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Dúplex en Calle de Sant Ramon, 197, Sant Ramón, Cerdanyola del Vallès</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Sant Ramon</t>
-        </is>
-      </c>
+          <t>Casa o chalet en Montflorit-Plana del Castell, Cerdanyola del Vallès</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
           <t>idealista_local</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>473000</v>
+        <v>440000</v>
       </c>
       <c r="E6" t="n">
-        <v>190</v>
+        <v>214</v>
       </c>
       <c r="F6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
@@ -1391,24 +1387,24 @@
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>exterior · luminoso · tranquilo · cerca FGC/tren · Calle de Sant Ramon</t>
+          <t>exterior · vistas · tranquilo</t>
         </is>
       </c>
       <c r="N6" t="n">
-        <v>0.572</v>
+        <v>0.431</v>
       </c>
       <c r="O6" t="n">
-        <v>59.9</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
@@ -1426,23 +1422,23 @@
         <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W6" t="n">
-        <v>526885</v>
+        <v>544769</v>
       </c>
       <c r="X6" t="n">
-        <v>-10.23</v>
+        <v>-19.23</v>
       </c>
       <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="n">
-        <v>0.8110000000000001</v>
+        <v>0.891</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.345</v>
+        <v>0.274</v>
       </c>
       <c r="AB6" t="n">
         <v>1</v>
@@ -1452,31 +1448,31 @@
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>0.687</t>
+          <t>0.694</t>
         </is>
       </c>
       <c r="AE6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AF6" t="n">
-        <v>455000</v>
+        <v>415000</v>
       </c>
       <c r="AG6" t="n">
-        <v>460000</v>
+        <v>425000</v>
       </c>
       <c r="AH6" t="n">
-        <v>465000</v>
+        <v>430000</v>
       </c>
       <c r="AI6" t="n">
-        <v>470000</v>
+        <v>435000</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>act fast (well-priced; open &lt;5% below)</t>
+          <t>standard (open ~5-8% below)</t>
         </is>
       </c>
       <c r="AK6" t="n">
-        <v>1358</v>
+        <v>1222</v>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
@@ -1495,20 +1491,20 @@
         <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>144900</v>
+        <v>133875</v>
       </c>
       <c r="AQ6" t="n">
         <v>0</v>
       </c>
       <c r="AR6" t="n">
-        <v>148050</v>
+        <v>137025</v>
       </c>
       <c r="AS6" t="n">
-        <v>1304</v>
+        <v>1160</v>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>✓ base 3% — descuento mediano que acaban aceptando los anuncios que se retiran del mercado; ✗ días online: solo 60 días (percentil 42%) — anuncio aún fresco, sin palanca (+0); ✗ bajadas de precio: ninguna observada todavía (+0); ✗ multi-agencia: solo lo vemos en una fuente (+0); ✗ relistado: no detectado (+0); ✗ reactivaciones: ninguna (+0); ✗ texto motivado: sin señales tipo herencia/urge/negociable (+0); ✗ sobreprecio: ya pide un 10% por DEBAJO de su valor de mercado — buen precio, poco recorrido extra (+0); ✓ el mercado en tu banda se está enfriando (buyer score alto) (+1%); POR QUÉ ESTÁ EN EL TOP (score 0.687): valor 0.81 (barato para lo que es) · palanca 0.34 (señales de negociación) · encaje cuota 1.00 · oportunidad de reforma ✓</t>
+          <t>✓ base 3% — descuento mediano que acaban aceptando los anuncios que se retiran del mercado; ✗ días online: solo 0 días (percentil 0%) — anuncio aún fresco, sin palanca (+0); ✗ bajadas de precio: ninguna observada todavía (+0); ✗ multi-agencia: solo lo vemos en una fuente (+0); ✗ relistado: no detectado (+0); ✗ reactivaciones: ninguna (+0); ✓ el texto del anuncio sugiere vendedor motivado (renovation) (+2%); ✗ sobreprecio: ya pide un 19% por DEBAJO de su valor de mercado — buen precio, poco recorrido extra (+0); ✓ el mercado en tu banda se está enfriando (buyer score alto) (+1%); POR QUÉ ESTÁ EN EL TOP (score 0.694): valor 0.89 (barato para lo que es) · palanca 0.27 (señales de negociación) · encaje cuota 1.00 · oportunidad de reforma ✓</t>
         </is>
       </c>
       <c r="AU6" t="n">
@@ -1519,35 +1515,39 @@
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>idealista_111357087</t>
+          <t>idealista_112182550</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>https://www.idealista.com/inmueble/111357087/</t>
+          <t>https://www.idealista.com/inmueble/112182550/</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Chalet pareado en Calle d'Anselm Clavé, Martinica-Ateneu, Cerdanyola del Vallès</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr"/>
+          <t>Dúplex en Calle de Sant Ramon, 197, Sant Ramón, Cerdanyola del Vallès</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Sant Ramon</t>
+        </is>
+      </c>
       <c r="C7" t="inlineStr">
         <is>
           <t>idealista_local</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>580000</v>
+        <v>473000</v>
       </c>
       <c r="E7" t="n">
-        <v>282</v>
+        <v>190</v>
       </c>
       <c r="F7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
@@ -1557,21 +1557,21 @@
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>cerca FGC/tren · Calle d'Anselm Clavé</t>
+          <t>exterior · luminoso · tranquilo · cerca FGC/tren · Calle de Sant Ramon</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0.445</v>
+        <v>0.572</v>
       </c>
       <c r="O7" t="n">
         <v>59.9</v>
@@ -1592,61 +1592,61 @@
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>650082</v>
+        <v>526885</v>
       </c>
       <c r="X7" t="n">
-        <v>-10.78</v>
+        <v>-10.23</v>
       </c>
       <c r="Y7" t="inlineStr"/>
       <c r="Z7" t="n">
-        <v>0.862</v>
+        <v>0.8110000000000001</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.495</v>
+        <v>0.345</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.642</v>
+        <v>1</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>0.678</t>
+          <t>0.687</t>
         </is>
       </c>
       <c r="AE7" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AF7" t="n">
-        <v>545000</v>
+        <v>455000</v>
       </c>
       <c r="AG7" t="n">
-        <v>560000</v>
+        <v>460000</v>
       </c>
       <c r="AH7" t="n">
-        <v>570000</v>
+        <v>465000</v>
       </c>
       <c r="AI7" t="n">
-        <v>570000</v>
+        <v>470000</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>standard (open ~5-8% below)</t>
+          <t>act fast (well-priced; open &lt;5% below)</t>
         </is>
       </c>
       <c r="AK7" t="n">
-        <v>1715</v>
+        <v>1358</v>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>con_extras</t>
+          <t>comfortable</t>
         </is>
       </c>
       <c r="AM7" t="n">
@@ -1654,50 +1654,50 @@
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>con_extras</t>
+          <t>comfortable</t>
         </is>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
       </c>
       <c r="AP7" t="n">
-        <v>176400</v>
+        <v>144900</v>
       </c>
       <c r="AQ7" t="n">
         <v>0</v>
       </c>
       <c r="AR7" t="n">
-        <v>179550</v>
+        <v>148050</v>
       </c>
       <c r="AS7" t="n">
-        <v>1656</v>
+        <v>1304</v>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>✓ base 3% — descuento mediano que acaban aceptando los anuncios que se retiran del mercado; ✗ días online: solo 60 días (percentil 42%) — anuncio aún fresco, sin palanca (+0); ✗ bajadas de precio: ninguna observada todavía (+0); ✗ multi-agencia: solo lo vemos en una fuente (+0); ✗ relistado: no detectado (+0); ✗ reactivaciones: ninguna (+0); ✓ el texto del anuncio sugiere vendedor motivado (investor) (+2%); ✗ sobreprecio: ya pide un 11% por DEBAJO de su valor de mercado — buen precio, poco recorrido extra (+0); ✓ el mercado en tu banda se está enfriando (buyer score alto) (+1%); POR QUÉ ESTÁ EN EL TOP (score 0.678): valor 0.86 (barato para lo que es) · palanca 0.49 (señales de negociación) · encaje cuota 0.64</t>
+          <t>✓ base 3% — descuento mediano que acaban aceptando los anuncios que se retiran del mercado; ✗ días online: solo 60 días (percentil 42%) — anuncio aún fresco, sin palanca (+0); ✗ bajadas de precio: ninguna observada todavía (+0); ✗ multi-agencia: solo lo vemos en una fuente (+0); ✗ relistado: no detectado (+0); ✗ reactivaciones: ninguna (+0); ✗ texto motivado: sin señales tipo herencia/urge/negociable (+0); ✗ sobreprecio: ya pide un 10% por DEBAJO de su valor de mercado — buen precio, poco recorrido extra (+0); ✓ el mercado en tu banda se está enfriando (buyer score alto) (+1%); POR QUÉ ESTÁ EN EL TOP (score 0.687): valor 0.81 (barato para lo que es) · palanca 0.34 (señales de negociación) · encaje cuota 1.00 · oportunidad de reforma ✓</t>
         </is>
       </c>
       <c r="AU7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV7" t="n">
         <v>1</v>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>idealista_110486816</t>
+          <t>idealista_111357087</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>https://www.idealista.com/inmueble/110486816/</t>
+          <t>https://www.idealista.com/inmueble/111357087/</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Casa o chalet en Montflorit-Plana del Castell, Cerdanyola del Vallès</t>
+          <t>Chalet pareado en Calle d'Anselm Clavé, Martinica-Ateneu, Cerdanyola del Vallès</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -1707,10 +1707,10 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>440000</v>
+        <v>580000</v>
       </c>
       <c r="E8" t="n">
-        <v>214</v>
+        <v>282</v>
       </c>
       <c r="F8" t="n">
         <v>4</v>
@@ -1733,14 +1733,14 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>tranquilo</t>
+          <t>cerca FGC/tren · Calle d'Anselm Clavé</t>
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0.431</v>
+        <v>0.445</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>59.9</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
@@ -1758,61 +1758,61 @@
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>544769</v>
+        <v>650082</v>
       </c>
       <c r="X8" t="n">
-        <v>-19.23</v>
+        <v>-10.78</v>
       </c>
       <c r="Y8" t="inlineStr"/>
       <c r="Z8" t="n">
-        <v>0.891</v>
+        <v>0.862</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.124</v>
+        <v>0.495</v>
       </c>
       <c r="AB8" t="n">
-        <v>1</v>
+        <v>0.642</v>
       </c>
       <c r="AC8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>0.649</t>
+          <t>0.678</t>
         </is>
       </c>
       <c r="AE8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AF8" t="n">
-        <v>420000</v>
+        <v>545000</v>
       </c>
       <c r="AG8" t="n">
-        <v>430000</v>
+        <v>560000</v>
       </c>
       <c r="AH8" t="n">
-        <v>435000</v>
+        <v>570000</v>
       </c>
       <c r="AI8" t="n">
-        <v>435000</v>
+        <v>570000</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>act fast (well-priced; open &lt;5% below)</t>
+          <t>standard (open ~5-8% below)</t>
         </is>
       </c>
       <c r="AK8" t="n">
-        <v>1222</v>
+        <v>1715</v>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>comfortable</t>
+          <t>con_extras</t>
         </is>
       </c>
       <c r="AM8" t="n">
@@ -1820,43 +1820,43 @@
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>comfortable</t>
+          <t>con_extras</t>
         </is>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>135450</v>
+        <v>176400</v>
       </c>
       <c r="AQ8" t="n">
         <v>0</v>
       </c>
       <c r="AR8" t="n">
-        <v>137025</v>
+        <v>179550</v>
       </c>
       <c r="AS8" t="n">
-        <v>1181</v>
+        <v>1656</v>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>✓ base 3% — descuento mediano que acaban aceptando los anuncios que se retiran del mercado; ✗ días online: solo 0 días (percentil 0%) — anuncio aún fresco, sin palanca (+0); ✗ bajadas de precio: ninguna observada todavía (+0); ✗ multi-agencia: solo lo vemos en una fuente (+0); ✗ relistado: no detectado (+0); ✗ reactivaciones: ninguna (+0); ✗ texto motivado: sin señales tipo herencia/urge/negociable (+0); ✗ sobreprecio: ya pide un 19% por DEBAJO de su valor de mercado — buen precio, poco recorrido extra (+0); ✓ el mercado en tu banda se está enfriando (buyer score alto) (+1%); POR QUÉ ESTÁ EN EL TOP (score 0.649): valor 0.89 (barato para lo que es) · palanca 0.12 (señales de negociación) · encaje cuota 1.00 · oportunidad de reforma ✓</t>
+          <t>✓ base 3% — descuento mediano que acaban aceptando los anuncios que se retiran del mercado; ✗ días online: solo 60 días (percentil 42%) — anuncio aún fresco, sin palanca (+0); ✗ bajadas de precio: ninguna observada todavía (+0); ✗ multi-agencia: solo lo vemos en una fuente (+0); ✗ relistado: no detectado (+0); ✗ reactivaciones: ninguna (+0); ✓ el texto del anuncio sugiere vendedor motivado (investor) (+2%); ✗ sobreprecio: ya pide un 11% por DEBAJO de su valor de mercado — buen precio, poco recorrido extra (+0); ✓ el mercado en tu banda se está enfriando (buyer score alto) (+1%); POR QUÉ ESTÁ EN EL TOP (score 0.678): valor 0.86 (barato para lo que es) · palanca 0.49 (señales de negociación) · encaje cuota 0.64</t>
         </is>
       </c>
       <c r="AU8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AV8" t="n">
         <v>1</v>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>idealista_112182550</t>
+          <t>idealista_110486816</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>https://www.idealista.com/inmueble/112182550/</t>
+          <t>https://www.idealista.com/inmueble/110486816/</t>
         </is>
       </c>
     </row>
@@ -12897,7 +12897,7 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>luminoso · tranquilo</t>
+          <t>exterior · luminoso · tranquilo</t>
         </is>
       </c>
       <c r="N74" t="n">
